--- a/output/pdf_financials_xlsx/PMZ.UN.xlsx
+++ b/output/pdf_financials_xlsx/PMZ.UN.xlsx
@@ -912,20 +912,14 @@
       <c r="C16" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1066,20 +1060,14 @@
       <c r="C20" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1168,20 +1156,14 @@
       <c r="C23" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -1332,20 +1314,14 @@
       <c r="C27" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1402,20 +1378,14 @@
       <c r="C29" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1449,15 +1419,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="3" t="n">
+        <v>15.83364048413608</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>28.24893171125131</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1482,20 +1448,14 @@
       <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -1529,15 +1489,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E32" s="3" t="n">
+        <v>15.83364048413608</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>28.24893171125131</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
@@ -3694,20 +3650,14 @@
       <c r="C99" s="3" t="n">
         <v>340.989</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-12.08</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>79.473</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>183.185</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
@@ -9027,7 +8977,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
         <v>-574.478</v>
       </c>
